--- a/artfynd/A 36372-2023 artfynd.xlsx
+++ b/artfynd/A 36372-2023 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>136488293</v>
       </c>
       <c r="B3" t="n">
-        <v>96927</v>
+        <v>96930</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 36372-2023 artfynd.xlsx
+++ b/artfynd/A 36372-2023 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>136488293</v>
       </c>
       <c r="B3" t="n">
-        <v>96930</v>
+        <v>96931</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 36372-2023 artfynd.xlsx
+++ b/artfynd/A 36372-2023 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>136488293</v>
       </c>
       <c r="B3" t="n">
-        <v>96931</v>
+        <v>96936</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 36372-2023 artfynd.xlsx
+++ b/artfynd/A 36372-2023 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>136488293</v>
       </c>
       <c r="B3" t="n">
-        <v>96936</v>
+        <v>96938</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 36372-2023 artfynd.xlsx
+++ b/artfynd/A 36372-2023 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>136488293</v>
       </c>
       <c r="B3" t="n">
-        <v>96938</v>
+        <v>96944</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 36372-2023 artfynd.xlsx
+++ b/artfynd/A 36372-2023 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>136488293</v>
       </c>
       <c r="B3" t="n">
-        <v>96944</v>
+        <v>96946</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 36372-2023 artfynd.xlsx
+++ b/artfynd/A 36372-2023 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>136488293</v>
       </c>
       <c r="B3" t="n">
-        <v>96946</v>
+        <v>96947</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 36372-2023 artfynd.xlsx
+++ b/artfynd/A 36372-2023 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>136488293</v>
       </c>
       <c r="B3" t="n">
-        <v>96947</v>
+        <v>96953</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 36372-2023 artfynd.xlsx
+++ b/artfynd/A 36372-2023 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>136488293</v>
       </c>
       <c r="B3" t="n">
-        <v>96953</v>
+        <v>96957</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
